--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1215</v>
+        <v>1171</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3513,14 +3513,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
         <v>42750000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>35185</v>
+        <v>36507</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>25号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5532,23 +5532,27 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3289</v>
+        <v>3350</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>162820000</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>49504</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5579,7 +5583,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5598,27 +5602,23 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3350</v>
+        <v>3304</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>146036800</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>44200</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3304</v>
+        <v>5260</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>146036800</v>
+        <v>260341664</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>44200</v>
+        <v>49495</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5734,23 +5734,27 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5260</v>
+        <v>3382</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>260341664</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>49495</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5759,12 +5763,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5774,14 +5778,14 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5800,27 +5804,23 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3382</v>
+        <v>2738</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>107460000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>39248</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5879,14 +5879,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>107460000</v>
+        <v>96136000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>39248</v>
+        <v>35099</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5936,23 +5936,27 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2739</v>
+        <v>3063</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>96136000</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>35099</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5961,12 +5965,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -5976,14 +5980,14 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6002,27 +6006,23 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>115238700</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>37150</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>35号屋</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6081,14 +6081,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>115238700</v>
+        <v>115840200</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>37150</v>
+        <v>37344</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>35号屋</t>
+          <t>36号屋</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6138,23 +6138,27 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>3102</v>
+        <v>3063</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>115840200</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>37344</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6163,12 +6167,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6178,14 +6182,14 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>36号屋</t>
+          <t>38号屋</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -6204,27 +6208,23 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>3063</v>
+        <v>4692</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>54561</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6247,72 +6247,6 @@
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>38号屋</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>4692</v>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>54561</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6625,10 +6559,10 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1215呎 (3房)
+          <t>B | 1171呎 (3房)
 $4275万
-$35,185/呎
-(26年-08月-11日)</t>
+$36,507/呎
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6854,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>32 套</t>
+          <t>31 套</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -6935,7 +6869,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>20 套</t>
+          <t>19 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -7193,16 +7127,7 @@
 $42,784/呎</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>25号屋
-3289呎 (4+房)
-(26年-07月-27日)
-$1.63亿
-$49,504/呎</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7211,7 +7136,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>27号屋
 3304呎 (4+房)
@@ -7220,7 +7145,7 @@
 $44,200/呎</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>28号屋
 5260呎 (4+房)
@@ -7229,14 +7154,7 @@
 $49,495/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7245,7 +7163,14 @@
 -</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
@@ -7254,7 +7179,7 @@
 $39,248/呎</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
@@ -7263,7 +7188,7 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7272,7 +7197,7 @@
 -</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>33号屋
 3102呎 (4+房)
@@ -7281,7 +7206,7 @@
 $37,150/呎</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>35号屋
 3102呎 (4+房)
@@ -7290,14 +7215,7 @@
 $37,344/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7306,7 +7224,14 @@
 -</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
@@ -7315,6 +7240,7 @@
 $54,561/呎</t>
         </is>
       </c>
+      <c r="C11" s="29" t="inlineStr"/>
       <c r="D11" s="29" t="inlineStr"/>
       <c r="E11" s="29" t="inlineStr"/>
       <c r="F11" s="29" t="inlineStr"/>
@@ -8284,7 +8210,7 @@
           <t>A | 844呎 (2房)
 $2398万
 $28,412/呎
-(26年-08月-17日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8292,7 +8218,7 @@
           <t>B | 834呎 (2房)
 $2342万
 $28,082/呎
-(26年-08月-17日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5513,7 +5513,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>25号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5532,27 +5532,23 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3350</v>
+        <v>3289</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>162820000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>49504</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5583,7 +5579,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5602,23 +5598,27 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3304</v>
+        <v>3350</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>146036800</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>44200</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>5260</v>
+        <v>3304</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>260341664</v>
+        <v>146036800</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>49495</v>
+        <v>44200</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5734,27 +5734,23 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>3382</v>
+        <v>5260</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>260341664</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>49495</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5763,12 +5759,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5778,14 +5774,14 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5804,23 +5800,27 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2738</v>
+        <v>3382</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>107460000</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>39248</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5879,14 +5879,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>96136000</v>
+        <v>107460000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>35099</v>
+        <v>39248</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5936,27 +5936,23 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>3063</v>
+        <v>2739</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>96136000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>35099</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5965,12 +5961,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -5980,14 +5976,14 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6006,23 +6002,27 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3102</v>
+        <v>3063</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>115238700</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>37150</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>35号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6081,14 +6081,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>115840200</v>
+        <v>115238700</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>37344</v>
+        <v>37150</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>36号屋</t>
+          <t>35号屋</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6138,27 +6138,23 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>115840200</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>37344</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6167,12 +6163,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6182,71 +6178,141 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>36号屋</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>3063</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
           <t>38号屋</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>4692</v>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>2025-11-07</t>
         </is>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H84" s="5" t="n">
         <v>256000000</v>
       </c>
-      <c r="I83" s="5" t="n">
+      <c r="I84" s="5" t="n">
         <v>54561</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6854,7 +6920,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>31 套</t>
+          <t>32 套</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -6869,7 +6935,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>20 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -7127,7 +7193,16 @@
 $42,784/呎</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>25号屋
+3289呎 (4+房)
+(26年-07月-27日)
+$1.63亿
+$49,504/呎</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7136,7 +7211,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>27号屋
 3304呎 (4+房)
@@ -7145,7 +7220,7 @@
 $44,200/呎</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>28号屋
 5260呎 (4+房)
@@ -7154,7 +7229,14 @@
 $49,495/呎</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7163,14 +7245,7 @@
 -</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
@@ -7179,7 +7254,7 @@
 $39,248/呎</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
@@ -7188,7 +7263,7 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7197,7 +7272,7 @@
 -</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>33号屋
 3102呎 (4+房)
@@ -7206,7 +7281,7 @@
 $37,150/呎</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>35号屋
 3102呎 (4+房)
@@ -7215,7 +7290,14 @@
 $37,344/呎</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7224,14 +7306,7 @@
 -</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
@@ -7240,7 +7315,6 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr"/>
       <c r="D11" s="29" t="inlineStr"/>
       <c r="E11" s="29" t="inlineStr"/>
       <c r="F11" s="29" t="inlineStr"/>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5804,23 +5804,19 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>146500000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>43318</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5829,12 +5825,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5844,7 +5840,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6568,27 +6564,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6634,12 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 2456呎 (4+房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6661,12 +6657,12 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -6925,7 +6921,7 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>4 套</t>
         </is>
       </c>
       <c r="C3" s="26" t="inlineStr">
@@ -6935,7 +6931,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>20 套</t>
+          <t>21 套</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -7236,13 +7232,13 @@
           <t>第 5 行</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
-(在售)
-招标项目
--</t>
+(26年-09月-11日)
+$1.47亿
+$43,318/呎</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -4325,7 +4325,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -7010,7 +7010,7 @@
         <is>
           <t>3号屋
 4662呎 (4+房)
-(26年-08月-26日)
+(26年-09月-15日)
 $2.49亿
 $53,445/呎</t>
         </is>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="C3" s="26" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>6 套</t>
         </is>
       </c>
     </row>
@@ -7033,13 +7033,13 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>7号屋
 4728呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+(在售)
+招标项目
+-</t>
         </is>
       </c>
     </row>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -2086,23 +2086,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>52040000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>28054</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2111,12 +2107,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2126,7 +2122,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6002,7 +5998,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6012,12 +6008,12 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -6027,12 +6023,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6042,7 +6038,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6917,7 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>4 套</t>
         </is>
       </c>
       <c r="C3" s="26" t="inlineStr">
@@ -6941,7 +6937,7 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>6 套</t>
+          <t>7 套</t>
         </is>
       </c>
     </row>
@@ -7259,13 +7255,13 @@
 $35,099/呎</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
-(在售)
-招标项目
--</t>
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -7656,7 +7652,7 @@
           <t>B | 2436呎 (4+房)
 $8468万
 $34,762/呎
-(26年-08月-28日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -8189,7 +8185,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8199,7 +8195,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8260,12 +8256,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1855呎 (4+房)
-招标单位
--
-(在售)</t>
+$5204万
+$28,054/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -138,7 +138,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3382</v>
+        <v>3307</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5805,14 +5805,14 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
         <v>146500000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>43318</v>
+        <v>44300</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6380,22 +6380,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -6463,7 +6463,7 @@
           <t>B | 2511呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
           <t>B | 1097呎 (3房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>
@@ -6560,22 +6560,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -6612,7 +6612,7 @@
           <t>A | 1170呎 (3房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6917,22 +6917,22 @@
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>21 套</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
           <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="27" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>0 套</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -7033,8 +7033,8 @@
         <is>
           <t>7号屋
 4728呎 (4+房)
-(在售)
-招标项目
+(暂停销售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7085,8 +7085,8 @@
         <is>
           <t>12号屋
 2716呎 (4+房)
-(在售)
-招标项目
+(暂停销售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7094,8 +7094,8 @@
         <is>
           <t>15号屋
 2695呎 (4+房)
-(在售)
-招标项目
+(暂停销售)
+招标单位
 -</t>
         </is>
       </c>
@@ -7231,10 +7231,10 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t>29号屋
-3382呎 (4+房)
-(26年-09月-11日)
+3307呎 (4+房)
+(26年-10月-14日)
 $1.47亿
-$43,318/呎</t>
+$44,300/呎</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -7293,8 +7293,8 @@
         <is>
           <t>36号屋
 3063呎 (4+房)
-(在售)
-招标项目
+(暂停销售)
+招标单位
 -</t>
         </is>
       </c>
@@ -8358,22 +8358,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8449,7 +8449,7 @@
           <t>A | 844呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -8261,7 +8261,7 @@
           <t>B | 1855呎 (4+房)
 $5204万
 $28,054/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>

--- a/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
+++ b/港岛-赤柱-One Stanley/One Stanley_销控明细表.xlsx
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2452</v>
+        <v>2566</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>86200000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>35155</v>
+        <v>33593</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2437</v>
+        <v>2551</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>85020000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>34887</v>
+        <v>33328</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2436</v>
+        <v>2466</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>84680000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>34762</v>
+        <v>34339</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3212</v>
+        <v>3337</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>119800000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>37298</v>
+        <v>35901</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3198</v>
+        <v>3341</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>127760000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>39950</v>
+        <v>38240</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1851</v>
+        <v>1909</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>73370000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>39638</v>
+        <v>38434</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1851</v>
+        <v>1909</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>61088000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>33003</v>
+        <v>32000</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1871</v>
+        <v>1919</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>67516975</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>36086</v>
+        <v>35183</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1855</v>
+        <v>1910</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>52040000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>28054</v>
+        <v>27246</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1874</v>
+        <v>1931</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1871</v>
+        <v>1919</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>77078792</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>41197</v>
+        <v>40166</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1171</v>
+        <v>1215</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>43820000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>37421</v>
+        <v>36066</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1170</v>
+        <v>1214</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43804800</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>37440</v>
+        <v>36083</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2511</v>
+        <v>2565</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>68120000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>27129</v>
+        <v>26558</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2403</v>
+        <v>2456</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1171</v>
+        <v>1215</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43800000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>37404</v>
+        <v>36049</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1170</v>
+        <v>1214</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>43804800</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>37440</v>
+        <v>36083</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2511</v>
+        <v>2565</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2403</v>
+        <v>2456</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1171</v>
+        <v>1215</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>42750000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>36507</v>
+        <v>35185</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1170</v>
+        <v>1214</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2437</v>
+        <v>2551</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>82231500</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>33743</v>
+        <v>32235</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2452</v>
+        <v>2566</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>87760000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>35791</v>
+        <v>34201</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2436</v>
+        <v>2466</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>87780000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>36034</v>
+        <v>35596</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2436</v>
+        <v>2466</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>86950000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>35694</v>
+        <v>35260</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4706</v>
+        <v>4732</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>268000000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>56949</v>
+        <v>56636</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4662</v>
+        <v>4689</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>249160000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>53445</v>
+        <v>53137</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4666</v>
+        <v>4693</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>246580000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>52846</v>
+        <v>52542</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5239</v>
+        <v>5301</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>322700000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>61596</v>
+        <v>60875</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3297</v>
+        <v>3336</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>151080000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>45823</v>
+        <v>45288</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3053</v>
+        <v>3075</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>116800000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>38257</v>
+        <v>37984</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3034</v>
+        <v>3059</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>118070000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38916</v>
+        <v>38598</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5509</v>
+        <v>5567</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>362500000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>65801</v>
+        <v>65116</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3436</v>
+        <v>3451</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>138000000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>40163</v>
+        <v>39988</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>3297</v>
+        <v>3314</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>138700000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>42069</v>
+        <v>41853</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>3285</v>
+        <v>3326</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>138000000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>42009</v>
+        <v>41491</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3272</v>
+        <v>3312</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>139988888</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>42784</v>
+        <v>42267</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3289</v>
+        <v>3331</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>162820000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>49504</v>
+        <v>48880</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5260</v>
+        <v>5329</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>260341664</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>49495</v>
+        <v>48854</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3307</v>
+        <v>3382</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>146500000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>44300</v>
+        <v>43318</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2738</v>
+        <v>2788</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>107460000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>39248</v>
+        <v>38544</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2739</v>
+        <v>2781</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>96136000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>35099</v>
+        <v>34569</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>3063</v>
+        <v>3097</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>4692</v>
+        <v>4725</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>256000000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>54561</v>
+        <v>54180</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6429,17 +6429,17 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1170呎 (3房)
+          <t>A | 1214呎 (3房)
 $4380万
-$37,440/呎
+$36,083/呎
 (25年-03月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1171呎 (3房)
+          <t>B | 1215呎 (3房)
 $4380万
-$37,404/呎
+$36,049/呎
 (25年-05月-15日)</t>
         </is>
       </c>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4+房)
+          <t>A | 2456呎 (4+房)
 -
 -
 (待售)</t>
@@ -6460,8 +6460,8 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 2511呎 (4+房)
-招标单位
+          <t>B | 2565呎 (4+房)
+-
 -
 (暂停销售)</t>
         </is>
@@ -6484,7 +6484,7 @@
       <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -6609,17 +6609,17 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>A | 1170呎 (3房)
-招标单位
+          <t>A | 1214呎 (3房)
+-
 -
 (暂停销售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1171呎 (3房)
+          <t>B | 1215呎 (3房)
 $4275万
-$36,507/呎
+$35,185/呎
 (26年-09月-04日)</t>
         </is>
       </c>
@@ -6803,17 +6803,17 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2452呎 (4+房)
+          <t>C | 2566呎 (4+房)
 $8776万
-$35,791/呎
+$34,201/呎
 (26年-06月-09日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2437呎 (4+房)
+          <t>D | 2551呎 (4+房)
 $8223万
-$33,743/呎
+$32,235/呎
 (25年-10月-08日)</t>
         </is>
       </c>
@@ -6826,17 +6826,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2436呎 (4+房)
+          <t>A | 2466呎 (4+房)
 $8695万
-$35,694/呎
+$35,260/呎
 (26年-08月-31日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2436呎 (4+房)
+          <t>B | 2466呎 (4+房)
 $8778万
-$36,034/呎
+$35,596/呎
 (25年-10月-31日)</t>
         </is>
       </c>
@@ -6996,28 +6996,28 @@
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>2号屋
-4706呎 (4+房)
+4732呎 (4+房)
 (26年-07月-07日)
 $2.68亿
-$56,949/呎</t>
+$56,636/呎</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t>3号屋
-4662呎 (4+房)
+4689呎 (4+房)
 (26年-09月-15日)
 $2.49亿
-$53,445/呎</t>
+$53,137/呎</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
           <t>5号屋
-4666呎 (4+房)
+4693呎 (4+房)
 (26年-02月-10日)
 $2.47亿
-$52,846/呎</t>
+$52,542/呎</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -7034,8 +7034,8 @@
           <t>7号屋
 4728呎 (4+房)
 (暂停销售)
-招标单位
--</t>
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
@@ -7066,19 +7066,19 @@
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t>10号屋
-5239呎 (4+房)
+5301呎 (4+房)
 (25年-12月-24日)
 $3.23亿
-$61,596/呎</t>
+$60,875/呎</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
           <t>11号屋
-3297呎 (4+房)
+3336呎 (4+房)
 (26年-08月-07日)
 $1.51亿
-$45,823/呎</t>
+$45,288/呎</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -7086,8 +7086,8 @@
           <t>12号屋
 2716呎 (4+房)
 (暂停销售)
-招标单位
--</t>
+暂无价格
+暂无呎价</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -7095,8 +7095,8 @@
           <t>15号屋
 2695呎 (4+房)
 (暂停销售)
-招标单位
--</t>
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
@@ -7109,28 +7109,28 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t>16号屋
-3053呎 (4+房)
+3075呎 (4+房)
 (26年-07月-13日)
 $1.17亿
-$38,257/呎</t>
+$37,984/呎</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
           <t>17号屋
-3034呎 (4+房)
+3059呎 (4+房)
 (26年-09月-02日)
 $1.18亿
-$38,916/呎</t>
+$38,598/呎</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t>18号屋
-5509呎 (4+房)
+5567呎 (4+房)
 (25年-12月-24日)
 $3.62亿
-$65,801/呎</t>
+$65,116/呎</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -7145,19 +7145,19 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t>20号屋
-3436呎 (4+房)
+3451呎 (4+房)
 (25年-07月-23日)
 $1.38亿
-$40,163/呎</t>
+$39,988/呎</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
           <t>21号屋
-3297呎 (4+房)
+3314呎 (4+房)
 (26年-04月-23日)
 $1.39亿
-$42,069/呎</t>
+$41,853/呎</t>
         </is>
       </c>
     </row>
@@ -7170,28 +7170,28 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t>22号屋
-3285呎 (4+房)
+3326呎 (4+房)
 (25年-10月-06日)
 $1.38亿
-$42,009/呎</t>
+$41,491/呎</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
           <t>23号屋
-3272呎 (4+房)
+3312呎 (4+房)
 (25年-09月-04日)
 $1.40亿
-$42,784/呎</t>
+$42,267/呎</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t>25号屋
-3289呎 (4+房)
+3331呎 (4+房)
 (26年-07月-27日)
 $1.63亿
-$49,504/呎</t>
+$48,880/呎</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -7215,10 +7215,10 @@
       <c r="G9" s="21" t="inlineStr">
         <is>
           <t>28号屋
-5260呎 (4+房)
+5329呎 (4+房)
 (25年-04月-08日)
 $2.60亿
-$49,495/呎</t>
+$48,854/呎</t>
         </is>
       </c>
     </row>
@@ -7231,34 +7231,34 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t>29号屋
-3307呎 (4+房)
+3382呎 (4+房)
 (26年-10月-14日)
 $1.47亿
-$44,300/呎</t>
+$43,318/呎</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
           <t>30号屋
-2738呎 (4+房)
+2788呎 (4+房)
 (26年-02月-13日)
 $1.07亿
-$39,248/呎</t>
+$38,544/呎</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t>31号屋
-2739呎 (4+房)
+2781呎 (4+房)
 (24年-11月-29日)
 $9,614万
-$35,099/呎</t>
+$34,569/呎</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
           <t>32号屋
-3063呎 (4+房)
+3102呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -7292,19 +7292,19 @@
       <c r="B11" s="23" t="inlineStr">
         <is>
           <t>36号屋
-3063呎 (4+房)
+3097呎 (4+房)
 (暂停销售)
-招标单位
--</t>
+暂无价格
+暂无呎价</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
           <t>38号屋
-4692呎 (4+房)
+4725呎 (4+房)
 (25年-11月-07日)
 $2.56亿
-$54,561/呎</t>
+$54,180/呎</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr"/>
@@ -7445,9 +7445,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2452呎 (4+房)
+          <t>C | 2566呎 (4+房)
 $8620万
-$35,155/呎
+$33,593/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -7626,9 +7626,9 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2437呎 (4+房)
+          <t>D | 2551呎 (4+房)
 $8502万
-$34,887/呎
+$33,328/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -7649,9 +7649,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2436呎 (4+房)
+          <t>B | 2466呎 (4+房)
 $8468万
-$34,762/呎
+$34,339/呎
 (26年-10月-02日)</t>
         </is>
       </c>
@@ -7778,9 +7778,9 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3212呎 (4+房)
+          <t>B | 3337呎 (4+房)
 $11980万
-$37,298/呎
+$35,901/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -7793,9 +7793,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 3198呎 (4+房)
+          <t>A | 3341呎 (4+房)
 $12776万
-$39,950/呎
+$38,240/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -7928,9 +7928,9 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1851呎 (4+房)
+          <t>B | 1909呎 (4+房)
 $7337万
-$39,638/呎
+$38,434/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -8085,9 +8085,9 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1851呎 (4+房)
+          <t>B | 1909呎 (4+房)
 $6109万
-$33,003/呎
+$32,000/呎
 (24年-05月-20日)</t>
         </is>
       </c>
@@ -8234,9 +8234,9 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1871呎 (4+房)
+          <t>A | 1919呎 (4+房)
 $6752万
-$36,086/呎
+$35,183/呎
 (24年-11月-14日)</t>
         </is>
       </c>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 1874呎 (4+房)
+          <t>A | 1931呎 (4+房)
 -
 -
 (待售)</t>
@@ -8258,9 +8258,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 1855呎 (4+房)
+          <t>B | 1910呎 (4+房)
 $5204万
-$28,054/呎
+$27,246/呎
 (26年-10月-20日)</t>
         </is>
       </c>
@@ -8408,9 +8408,9 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1871呎 (4+房)
+          <t>B | 1919呎 (4+房)
 $7708万
-$41,197/呎
+$40,166/呎
 (25年-02月-18日)</t>
         </is>
       </c>
@@ -8447,7 +8447,7 @@
       <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 844呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -8580,17 +8580,17 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1170呎 (3房)
+          <t>A | 1214呎 (3房)
 $4380万
-$37,440/呎
+$36,083/呎
 (25年-07月-22日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1171呎 (3房)
+          <t>B | 1215呎 (3房)
 $4382万
-$37,421/呎
+$36,066/呎
 (26年-05月-11日)</t>
         </is>
       </c>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4+房)
+          <t>A | 2456呎 (4+房)
 -
 -
 (待售)</t>
@@ -8611,9 +8611,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2511呎 (4+房)
+          <t>B | 2565呎 (4+房)
 $6812万
-$27,129/呎
+$26,558/呎
 (26年-05月-11日)</t>
         </is>
       </c>
